--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C436"/>
+  <dimension ref="A1:C476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AKSHARCHEM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,82 +446,82 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AONESTEELS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>AYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>DBSTOCKBRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ELEVATE</t>
+          <t>DIGJAMLMTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -548,48 +548,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,14 +599,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -616,14 +616,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -633,31 +633,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>MARATHON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>MHRIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,48 +667,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MELSTAR</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -718,31 +718,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>RAJRATAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -752,31 +752,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -786,14 +786,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>SWASTIKAIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -803,14 +803,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TATVA</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -820,14 +820,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>WAAREEINDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -837,14 +837,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>WENDT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VARMORA</t>
+          <t>ACCELYA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -888,48 +888,48 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Results/Stock split/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>BANSALWIRE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SRTL</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -939,48 +939,48 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -990,48 +990,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ADOR</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1041,48 +1041,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1092,14 +1092,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1109,31 +1109,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>HATSUN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1143,14 +1143,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MARATHON</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1177,14 +1177,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MHRIL</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1194,48 +1194,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1245,31 +1245,31 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RAJRATAN</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1279,31 +1279,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1313,31 +1313,31 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SWASTIKAIN</t>
+          <t>PITTIENG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1347,31 +1347,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WAAREEINDO</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WENDT</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1381,19 +1381,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ACCELYA</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>TTML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1456,12 +1456,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1490,24 +1490,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>ASAL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1517,99 +1517,99 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1619,65 +1619,65 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1687,31 +1687,31 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1738,14 +1738,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>GEOJITFSL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1755,14 +1755,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1772,31 +1772,31 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1806,14 +1806,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1823,48 +1823,48 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PITTIENG</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1874,31 +1874,31 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1908,99 +1908,99 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TTML</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>NAVKARCORP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2010,14 +2010,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASAL</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CMPDI</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>SBIFUNDS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GEOJITFSL</t>
+          <t>SHREDIGCEM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,12 +2306,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TIKONA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,7 +2442,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NAVKARCORP</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>TRIVENIPT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2554,48 +2554,48 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SBIFUNDS</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHREDIGCEM</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2639,31 +2639,31 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2673,82 +2673,82 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TIKONA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2758,65 +2758,65 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TRIVENIPT</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2860,48 +2860,48 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2928,14 +2928,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2945,14 +2945,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2962,14 +2962,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2979,14 +2979,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2996,133 +2996,133 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3132,48 +3132,48 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3200,36 +3200,36 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3292,7 +3292,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3326,7 +3326,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3360,7 +3360,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3377,12 +3377,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3513,7 +3513,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3530,7 +3530,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3598,7 +3598,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3608,14 +3608,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3676,14 +3676,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3693,31 +3693,31 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3836,7 +3836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3955,12 +3955,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4057,12 +4057,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4108,12 +4108,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4125,12 +4125,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4142,12 +4142,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4193,12 +4193,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4210,12 +4210,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4227,7 +4227,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4278,12 +4278,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4295,12 +4295,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4312,12 +4312,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -4329,12 +4329,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4380,7 +4380,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4390,14 +4390,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4465,7 +4465,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -4516,7 +4516,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4533,12 +4533,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4550,7 +4550,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4567,12 +4567,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4584,12 +4584,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -4601,12 +4601,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4686,7 +4686,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4771,12 +4771,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4788,12 +4788,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4839,7 +4839,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4890,7 +4890,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4941,7 +4941,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4951,14 +4951,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4985,31 +4985,31 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5019,14 +5019,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5036,14 +5036,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5087,36 +5087,36 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5128,7 +5128,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5213,12 +5213,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5230,7 +5230,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5264,12 +5264,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5281,12 +5281,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -5298,7 +5298,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5315,12 +5315,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -5332,12 +5332,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -5349,7 +5349,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5400,12 +5400,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5417,7 +5417,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5478,14 +5478,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5495,14 +5495,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5512,14 +5512,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5529,48 +5529,48 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5580,31 +5580,31 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5614,31 +5614,31 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5648,48 +5648,48 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5699,14 +5699,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5716,31 +5716,31 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5750,14 +5750,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5767,14 +5767,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5808,12 +5808,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -5825,12 +5825,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5869,14 +5869,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5903,31 +5903,31 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5988,14 +5988,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6005,48 +6005,48 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6056,48 +6056,48 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6107,31 +6107,31 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6158,14 +6158,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6192,14 +6192,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6209,14 +6209,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6243,14 +6243,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6260,14 +6260,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6294,31 +6294,31 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6328,48 +6328,48 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,82 +6430,82 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6532,48 +6532,48 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6583,14 +6583,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6600,14 +6600,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6651,65 +6651,65 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,31 +6719,31 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6753,14 +6753,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6770,48 +6770,48 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6838,82 +6838,82 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,65 +6923,65 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -7008,14 +7008,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7025,14 +7025,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,14 +7042,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7076,31 +7076,31 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -7161,31 +7161,31 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7212,31 +7212,31 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7246,31 +7246,31 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7280,31 +7280,31 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7314,82 +7314,82 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7399,14 +7399,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -7416,31 +7416,31 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7450,31 +7450,31 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -7501,31 +7501,31 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>ESABINDIA</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,31 +7535,31 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -7586,14 +7586,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>JTEKTINDIA</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7620,14 +7620,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7637,14 +7637,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7654,14 +7654,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7671,48 +7671,48 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7739,31 +7739,31 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7773,31 +7773,31 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>RUSTOMJEE</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7807,22 +7807,702 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>GAYAHWS</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>GUJENERGY</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>MUTHOOTCAP</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>BANCOINDIA</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>KCP</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>SUPRAJIT</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CENTRUM</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C476"/>
+  <dimension ref="A1:C491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2153,12 +2153,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBIFUNDS</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>SBIFUNDS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SHREDIGCEM</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SHREDIGCEM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,12 +2306,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2340,12 +2340,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TIKONA</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>TIKONA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TRIVENIPT</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>TRIVENIPT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2554,14 +2554,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2714,12 +2714,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2748,12 +2748,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,7 +2833,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,29 +2884,29 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,7 +3122,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,12 +3156,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3326,7 +3326,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3360,7 +3360,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3496,12 +3496,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -3513,12 +3513,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3530,7 +3530,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3598,46 +3598,46 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3666,12 +3666,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,7 +3700,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3717,7 +3717,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3785,12 +3785,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3836,12 +3836,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3955,7 +3955,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MARALOVER</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4108,12 +4108,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4125,12 +4125,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4142,12 +4142,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4193,12 +4193,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4244,12 +4244,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4261,7 +4261,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4295,7 +4295,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4312,12 +4312,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -4329,12 +4329,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4380,7 +4380,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4397,7 +4397,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4407,31 +4407,31 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4441,48 +4441,48 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4543,14 +4543,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4567,12 +4567,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4584,7 +4584,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4601,12 +4601,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4669,12 +4669,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -4686,7 +4686,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,12 +4737,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4771,12 +4771,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4788,7 +4788,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4890,7 +4890,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4941,12 +4941,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -4958,7 +4958,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4975,7 +4975,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5009,7 +5009,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5043,7 +5043,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5060,12 +5060,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5077,7 +5077,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5121,31 +5121,31 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5155,14 +5155,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5172,31 +5172,31 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5223,14 +5223,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5274,36 +5274,36 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -5315,7 +5315,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5332,12 +5332,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -5349,7 +5349,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5366,12 +5366,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5400,12 +5400,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5417,7 +5417,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5434,12 +5434,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5468,12 +5468,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5519,12 +5519,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -5536,12 +5536,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -5570,7 +5570,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5587,12 +5587,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -5604,7 +5604,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -5638,12 +5638,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -5655,12 +5655,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5689,7 +5689,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5706,7 +5706,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5723,12 +5723,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -5740,12 +5740,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5774,12 +5774,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -5791,7 +5791,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5801,31 +5801,31 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5835,48 +5835,48 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5995,7 +5995,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6114,12 +6114,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6165,7 +6165,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6182,7 +6182,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6216,12 +6216,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -6250,12 +6250,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6311,48 +6311,48 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6362,14 +6362,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,31 +6430,31 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6464,19 +6464,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -6505,7 +6505,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6522,7 +6522,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6539,41 +6539,41 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6583,14 +6583,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6600,14 +6600,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6651,14 +6651,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6685,31 +6685,31 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,36 +6719,36 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -6760,12 +6760,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -6777,7 +6777,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6794,12 +6794,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -6811,7 +6811,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6828,7 +6828,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6862,12 +6862,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -6879,12 +6879,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6913,7 +6913,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,65 +6923,65 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6991,31 +6991,31 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7025,14 +7025,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,14 +7042,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7059,31 +7059,31 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7093,14 +7093,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7134,12 +7134,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -7151,12 +7151,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -7168,12 +7168,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -7185,12 +7185,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -7202,7 +7202,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7219,12 +7219,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -7236,7 +7236,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7253,12 +7253,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -7270,7 +7270,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7287,7 +7287,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7304,7 +7304,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7321,7 +7321,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,48 +7331,48 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,14 +7382,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7399,82 +7399,82 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -7501,31 +7501,31 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,19 +7535,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -7559,12 +7559,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -7576,12 +7576,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7610,7 +7610,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7627,7 +7627,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -7661,7 +7661,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7678,12 +7678,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -7695,12 +7695,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7729,12 +7729,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ESABINDIA</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -7746,12 +7746,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -7763,12 +7763,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -7780,12 +7780,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -7797,12 +7797,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -7814,7 +7814,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -7831,7 +7831,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7848,7 +7848,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>JTEKTINDIA</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7865,7 +7865,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,31 +7909,31 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,31 +7943,31 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7977,99 +7977,99 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>RUSTOMJEE</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,14 +8096,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -8120,7 +8120,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -8137,12 +8137,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -8154,24 +8154,24 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>GUJENERGY</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>INSECTICID</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -8198,14 +8198,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -8232,31 +8232,31 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -8266,14 +8266,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>MUTHOOTCAP</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,31 +8283,31 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -8334,14 +8334,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -8368,65 +8368,65 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -8436,31 +8436,31 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -8470,39 +8470,294 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>KCP</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>SUPRAJIT</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>CENTRUM</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C491"/>
+  <dimension ref="A1:C466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>ACCELYA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,14 +446,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,31 +463,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADOR</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>BANSALWIRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,65 +497,65 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -565,14 +565,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -582,82 +582,82 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MARATHON</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MHRIL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,48 +667,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>HATSUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -718,14 +718,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RAJRATAN</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -735,48 +735,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -786,31 +786,31 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SWASTIKAIN</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -820,31 +820,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WAAREEINDO</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WENDT</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ACCELYA</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>PITTIENG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>TTML</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1065,24 +1065,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>ASAL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1143,14 +1143,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1160,31 +1160,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1194,82 +1194,82 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1279,14 +1279,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1296,14 +1296,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1313,31 +1313,31 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PITTIENG</t>
+          <t>GEOJITFSL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1347,31 +1347,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1381,65 +1381,65 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TTML</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1449,31 +1449,31 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1483,14 +1483,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASAL</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1524,12 +1524,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1541,12 +1541,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>NAVKARCORP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CMPDI</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1728,12 +1728,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GEOJITFSL</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1779,12 +1779,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SBIFUNDS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1830,12 +1830,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHREDIGCEM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>TIKONA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NAVKARCORP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>TRIVENIPT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2146,48 +2146,48 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2197,82 +2197,82 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBIFUNDS</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHREDIGCEM</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2282,31 +2282,31 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2316,65 +2316,65 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2384,31 +2384,31 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TIKONA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2418,14 +2418,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2435,65 +2435,65 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TRIVENIPT</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2520,31 +2520,31 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2554,14 +2554,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2588,14 +2588,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2605,48 +2605,48 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2656,31 +2656,31 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2724,48 +2724,48 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2775,31 +2775,31 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2809,31 +2809,31 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2860,53 +2860,53 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,7 +3122,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3234,31 +3234,31 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3285,31 +3285,31 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3319,14 +3319,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3353,82 +3353,82 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3438,31 +3438,31 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3472,82 +3472,82 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3574,14 +3574,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3591,48 +3591,48 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3649,12 +3649,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3666,12 +3666,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,12 +3700,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3751,7 +3751,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3785,12 +3785,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3836,12 +3836,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3904,12 +3904,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3955,12 +3955,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,12 +4040,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4125,41 +4125,41 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARALOVER</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4220,48 +4220,48 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4271,31 +4271,31 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4305,65 +4305,65 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4390,14 +4390,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4407,31 +4407,31 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4441,48 +4441,48 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4509,31 +4509,31 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4543,14 +4543,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4567,7 +4567,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4584,7 +4584,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4686,12 +4686,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,12 +4737,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4771,12 +4771,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4788,7 +4788,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4822,12 +4822,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,24 +4873,24 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4900,14 +4900,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4951,14 +4951,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5002,31 +5002,31 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5036,31 +5036,31 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5087,65 +5087,65 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5155,31 +5155,31 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5223,48 +5223,48 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5274,14 +5274,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5315,12 +5315,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -5332,7 +5332,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5349,12 +5349,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -5366,12 +5366,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -5383,12 +5383,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -5400,12 +5400,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5417,12 +5417,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5468,12 +5468,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5519,12 +5519,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5553,7 +5553,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5563,14 +5563,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5580,31 +5580,31 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5614,14 +5614,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5631,14 +5631,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5648,31 +5648,31 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5699,14 +5699,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5716,48 +5716,48 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5767,65 +5767,65 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5835,48 +5835,48 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5886,31 +5886,31 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5995,7 +5995,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6012,7 +6012,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6056,14 +6056,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6090,14 +6090,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6107,31 +6107,31 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6158,14 +6158,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6192,14 +6192,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6209,31 +6209,31 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6243,14 +6243,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6260,31 +6260,31 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6311,14 +6311,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6328,31 +6328,31 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6362,14 +6362,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,48 +6430,48 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6498,31 +6498,31 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6532,31 +6532,31 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6566,31 +6566,31 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6600,14 +6600,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6634,31 +6634,31 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6668,48 +6668,48 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,65 +6719,65 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6838,14 +6838,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6855,14 +6855,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6872,31 +6872,31 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6906,14 +6906,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,14 +6923,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6957,14 +6957,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6974,65 +6974,65 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,48 +7042,48 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7093,14 +7093,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,65 +7127,65 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7212,31 +7212,31 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7246,48 +7246,48 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7297,31 +7297,31 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>ESABINDIA</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,48 +7331,48 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,14 +7382,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7399,31 +7399,31 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>JTEKTINDIA</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7433,31 +7433,31 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7467,48 +7467,48 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -7518,14 +7518,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -7559,7 +7559,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7576,12 +7576,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -7593,12 +7593,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -7610,12 +7610,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>RUSTOMJEE</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -7627,7 +7627,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -7661,7 +7661,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7678,41 +7678,41 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7722,31 +7722,31 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>GUJENERGY</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7756,31 +7756,31 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>INSECTICID</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7790,14 +7790,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7807,31 +7807,31 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>MUTHOOTCAP</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7858,31 +7858,31 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,31 +7909,31 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,14 +7943,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7960,31 +7960,31 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7994,14 +7994,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -8011,48 +8011,48 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -8062,14 +8062,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,14 +8096,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -8113,14 +8113,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>KCP</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -8130,14 +8130,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,48 +8181,48 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>SUPRAJIT</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-11</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -8232,31 +8232,31 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>PGHH</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -8266,14 +8266,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>REGENCERAM</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,48 +8283,48 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>CENTRUM</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>GILLETTE</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -8333,431 +8333,6 @@
         </is>
       </c>
       <c r="C466" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>UGROCAP</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>3MINDIA</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>BANCOINDIA</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>CARRARO</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>CHOLAHLDNG</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>KCP</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>RAIN</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>TREJHARA</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>TTKPRESTIG</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>SUPRAJIT</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>MUKANDLTD</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>PGHH</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>REGENCERAM</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>CENTRUM</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>GILLETTE</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C466"/>
+  <dimension ref="A1:C575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PITTIENG</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>PITTIENG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -980,12 +980,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TTML</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1031,12 +1031,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>TTML</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1075,14 +1075,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASAL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>ASAL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1116,12 +1116,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CMPDI</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GEOJITFSL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>GEOJITFSL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1541,12 +1541,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NAVKARCORP</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>NAVKARCORP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1626,7 +1626,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1694,12 +1694,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1728,12 +1728,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1779,12 +1779,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SBIFUNDS</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>SBIFUNDS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHREDIGCEM</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SHREDIGCEM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TIKONA</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>TIKONA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TRIVENIPT</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>TRIVENIPT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2146,14 +2146,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2272,7 +2272,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,12 +2306,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2340,12 +2340,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2476,24 +2476,24 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2503,53 +2503,53 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,12 +2629,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2748,12 +2748,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2901,12 +2901,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,24 +3207,24 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3234,31 +3234,31 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3285,31 +3285,31 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3319,116 +3319,116 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3455,31 +3455,31 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3489,53 +3489,53 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3581,7 +3581,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3615,7 +3615,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3649,12 +3649,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3666,7 +3666,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,12 +3700,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MARALOVER</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3785,12 +3785,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3836,7 +3836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3904,12 +3904,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3938,12 +3938,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3955,7 +3955,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,12 +4040,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4125,41 +4125,41 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4220,48 +4220,48 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4271,65 +4271,65 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4339,31 +4339,31 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4390,48 +4390,48 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4458,31 +4458,31 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4492,65 +4492,65 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4560,65 +4560,65 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4628,14 +4628,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4662,14 +4662,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4679,19 +4679,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4754,12 +4754,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4788,12 +4788,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4822,12 +4822,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -4839,7 +4839,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,24 +4873,24 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4900,14 +4900,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4951,14 +4951,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5002,31 +5002,31 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5036,31 +5036,31 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5087,31 +5087,31 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5121,14 +5121,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5155,48 +5155,48 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5223,31 +5223,31 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5274,14 +5274,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5291,31 +5291,31 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5342,31 +5342,31 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5393,65 +5393,65 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5478,31 +5478,31 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5512,14 +5512,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5546,82 +5546,82 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5631,48 +5631,48 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>SHILCTECH</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5699,14 +5699,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>SNOWMAN</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5716,14 +5716,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5750,14 +5750,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5767,48 +5767,48 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5818,31 +5818,31 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5869,65 +5869,65 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5954,31 +5954,31 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5988,14 +5988,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -6005,31 +6005,31 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6039,31 +6039,31 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6090,14 +6090,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6107,48 +6107,48 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6158,31 +6158,31 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6192,14 +6192,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6209,31 +6209,31 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6243,48 +6243,48 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6294,82 +6294,82 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>FIBERWEB</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>HORIZONIND</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6498,48 +6498,48 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6549,65 +6549,65 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6651,31 +6651,31 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6685,31 +6685,31 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,31 +6719,31 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6753,31 +6753,31 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>SURAJLTD</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6838,31 +6838,31 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6872,14 +6872,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6906,14 +6906,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,48 +6923,48 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6974,65 +6974,65 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,31 +7042,31 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7076,14 +7076,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7093,14 +7093,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,48 +7127,48 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -7178,14 +7178,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7212,65 +7212,65 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7280,14 +7280,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7297,31 +7297,31 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,31 +7331,31 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -7365,14 +7365,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,65 +7382,65 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>NAHARPOLY</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>NAHARSPING</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7467,14 +7467,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,31 +7484,31 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -7518,14 +7518,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,48 +7535,48 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -7586,48 +7586,48 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7637,14 +7637,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7654,31 +7654,31 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7688,14 +7688,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7739,14 +7739,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7756,31 +7756,31 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7790,31 +7790,31 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7858,48 +7858,48 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,14 +7943,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7960,82 +7960,82 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -8045,31 +8045,31 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,14 +8096,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -8113,14 +8113,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -8130,31 +8130,31 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -8198,48 +8198,48 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -8266,14 +8266,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,14 +8283,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -8300,39 +8300,1892 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
+          <t>ARVEE</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ASKAUTOLTD</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>DNAMEDIA</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>EMCURE</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ENDURANCE</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>FRACTAL</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>GLAXO</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>GSPLTRANS</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>HARSHA</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>LUXIND</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>MIRZAINT</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>NXST</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>PUNJABCHEM</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>RBZJEWEL</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>RML</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>RUSHIL</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>SERVOTECH</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>ALLTIME</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ASHIANA</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>BASF</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>CARYSIL</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ESABINDIA</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend/Other business matters</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>JMFINANCIL</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>JTEKTINDIA</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>JYOTHYLAB</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>KANSAINER</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>KSHINTL</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>RUSTOMJEE</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>UNIVCABLES</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>GAYAHWS</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>GUJENERGY</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>MUTHOOTCAP</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>BANCOINDIA</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>KCP</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>TRANSWORLD</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>SUPRAJIT</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>CENTRUM</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C575"/>
+  <dimension ref="A1:C537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACCELYA</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,14 +446,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ASAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,48 +463,48 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -514,48 +514,48 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -565,99 +565,99 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,14 +667,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -684,14 +684,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>GEOJITFSL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -701,14 +701,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -718,14 +718,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -735,31 +735,31 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -769,48 +769,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -820,48 +820,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -871,31 +871,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -905,31 +905,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PITTIENG</t>
+          <t>MAHLOG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -939,31 +939,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>NAVKARCORP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -973,31 +973,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>NEWGEN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1007,31 +1007,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TTML</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1041,14 +1041,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1075,14 +1075,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>RUNWALENTR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASAL</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1116,12 +1116,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>SBIFUNDS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SHREDIGCEM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CMPDI</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>SKMEGGPROD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEOJITFSL</t>
+          <t>TIKONA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TRIVENIPT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1517,31 +1517,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1551,31 +1551,31 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1585,14 +1585,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAVKARCORP</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1602,31 +1602,31 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1636,31 +1636,31 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1670,14 +1670,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1704,31 +1704,31 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RUNWALENTR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1738,14 +1738,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1755,31 +1755,31 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SBIFUNDS</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1806,31 +1806,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1840,14 +1840,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHREDIGCEM</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1857,48 +1857,48 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SKMEGGPROD</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1908,48 +1908,48 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1959,14 +1959,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1976,14 +1976,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TIKONA</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2010,31 +2010,31 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2044,14 +2044,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2061,14 +2061,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TRIVENIPT</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2078,14 +2078,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2095,14 +2095,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UNIECOM</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2112,48 +2112,48 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2180,31 +2180,31 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2214,14 +2214,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2231,14 +2231,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2248,31 +2248,31 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2282,31 +2282,31 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2333,82 +2333,82 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2418,14 +2418,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2435,31 +2435,31 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2469,31 +2469,31 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2503,53 +2503,53 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2894,48 +2894,48 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2945,14 +2945,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2962,14 +2962,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2979,14 +2979,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2996,14 +2996,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3013,31 +3013,31 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3064,116 +3064,116 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3200,31 +3200,31 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3234,14 +3234,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3285,14 +3285,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3319,65 +3319,65 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3421,31 +3421,31 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3455,82 +3455,82 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3615,7 +3615,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3649,12 +3649,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3666,7 +3666,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CINEVISTA</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,7 +3700,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3785,12 +3785,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3836,7 +3836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,12 +3887,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3938,12 +3938,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3955,12 +3955,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4050,14 +4050,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4067,31 +4067,31 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4101,65 +4101,65 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARALOVER</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4220,48 +4220,48 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4288,31 +4288,31 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4356,31 +4356,31 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4390,31 +4390,31 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4424,14 +4424,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4458,31 +4458,31 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SECMARK</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4492,31 +4492,31 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4526,31 +4526,31 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4560,65 +4560,65 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4628,14 +4628,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4662,31 +4662,31 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,12 +4737,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -4754,12 +4754,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4788,12 +4788,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>APCOTEXIND</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4890,7 +4890,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BOROSCI</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4941,12 +4941,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CHEMFAB</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -4975,7 +4975,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4992,12 +4992,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5009,7 +5009,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>SHILCTECH</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5043,12 +5043,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5060,7 +5060,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>SNOWMAN</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5077,7 +5077,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5230,12 +5230,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -5247,7 +5247,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5264,12 +5264,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5298,7 +5298,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5308,31 +5308,31 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5376,48 +5376,48 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5427,14 +5427,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5478,31 +5478,31 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5512,31 +5512,31 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5546,31 +5546,31 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5580,14 +5580,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5597,31 +5597,31 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5631,31 +5631,31 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>FIBERWEB</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5665,14 +5665,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SHILCTECH</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5699,31 +5699,31 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SNOWMAN</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5750,14 +5750,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5767,65 +5767,65 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>HORIZONIND</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5835,14 +5835,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5869,31 +5869,31 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5903,31 +5903,31 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5937,19 +5937,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -6097,12 +6097,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -6114,12 +6114,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -6131,12 +6131,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>SURAJLTD</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6165,12 +6165,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -6182,7 +6182,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6199,12 +6199,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -6216,12 +6216,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6284,7 +6284,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>FIBERWEB</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6328,14 +6328,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6345,31 +6345,31 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>HORIZONIND</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6447,31 +6447,31 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6515,31 +6515,31 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6549,31 +6549,31 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6583,31 +6583,31 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,65 +6617,65 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6685,31 +6685,31 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,31 +6719,31 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>NAHARPOLY</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6753,48 +6753,48 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>NAHARSPING</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SURAJLTD</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6838,31 +6838,31 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6872,14 +6872,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6889,31 +6889,31 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,14 +6923,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6940,31 +6940,31 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6991,48 +6991,48 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,14 +7042,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7076,14 +7076,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7093,14 +7093,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -7144,48 +7144,48 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7212,31 +7212,31 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7246,14 +7246,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7263,31 +7263,31 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7297,14 +7297,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,14 +7331,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7348,31 +7348,31 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>NAHARCAP</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,31 +7382,31 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>NAHARPOLY</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>NAHARSPING</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -7416,31 +7416,31 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7467,14 +7467,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,31 +7484,31 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -7518,14 +7518,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,31 +7535,31 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7569,31 +7569,31 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7620,14 +7620,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7637,14 +7637,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7654,65 +7654,65 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7739,14 +7739,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7756,14 +7756,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7790,48 +7790,48 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7858,31 +7858,31 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7892,14 +7892,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>MIRZAINT</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,31 +7943,31 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7977,65 +7977,65 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -8045,31 +8045,31 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,65 +8096,65 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>ASHIANA</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -8198,82 +8198,82 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,31 +8283,31 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>ESABINDIA</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -8317,48 +8317,48 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -8368,14 +8368,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -8385,14 +8385,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -8419,14 +8419,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>JTEKTINDIA</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -8436,14 +8436,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -8453,14 +8453,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -8470,14 +8470,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -8487,31 +8487,31 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -8521,31 +8521,31 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -8555,31 +8555,31 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>MIRZAINT</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -8589,31 +8589,31 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -8623,65 +8623,65 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>RUSTOMJEE</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -8708,14 +8708,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>UNIVCABLES</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -8725,14 +8725,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>VINDHYATEL</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -8749,12 +8749,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -8766,24 +8766,24 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>AMAGI</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ASHIANA</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -8810,14 +8810,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -8827,14 +8827,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>GUJENERGY</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -8844,116 +8844,116 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>INSECTICID</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>MUTHOOTCAP</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -8963,48 +8963,48 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -9014,14 +9014,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -9031,14 +9031,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -9048,14 +9048,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -9065,48 +9065,48 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>UGROCAP</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -9116,48 +9116,48 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>COFFEEDAY</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -9184,14 +9184,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -9201,31 +9201,31 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -9235,14 +9235,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>KCP</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -9252,14 +9252,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -9269,14 +9269,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>TRANSWORLD</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -9286,31 +9286,31 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -9320,14 +9320,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>WSTCSTPAPR</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -9337,31 +9337,31 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>GOLDIAM</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>UNIVCABLES</t>
+          <t>SUPRAJIT</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -9371,31 +9371,31 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>PGHH</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -9422,14 +9422,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>RANEHOLDIN</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>REGENCERAM</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -9473,31 +9473,31 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>CENTRUM</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>GILLETTE</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -9507,14 +9507,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>JAICORPLTD</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -9524,14 +9524,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>MTNL</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -9540,652 +9540,6 @@
         </is>
       </c>
       <c r="C537" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>MUTHOOTCAP</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>ORIENTPPR</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>PRAXIS</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>SAILIFE</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>UGROCAP</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>3MINDIA</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>BANCOINDIA</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>CARRARO</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>CHOLAHLDNG</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>COFFEEDAY</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>FOSECOIND</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>KCP</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>RAIN</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>TRANSWORLD</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Financial Results/Dividend</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>TREJHARA</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>TTKPRESTIG</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>WSTCSTPAPR</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>GOLDIAM</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Financial Results/Dividend</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>SUPRAJIT</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>MUKANDLTD</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>PGHH</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>RANEHOLDIN</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>REGENCERAM</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>CENTRUM</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>GILLETTE</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>JAICORPLTD</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>Financial Results/Other business matters</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>MTNL</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C537"/>
+  <dimension ref="A1:C656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,12 +1881,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1898,29 +1898,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ACEVECTOR</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>ACEVECTOR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BRIGHOTEL</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>BRIGHOTEL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEEPA</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>DEEPA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GENUSPOWER</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>GENUSPOWER</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LEAPIND</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LUMAXIND</t>
+          <t>LEAPIND</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2391,12 +2391,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>LUMAXIND</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2442,7 +2442,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2527,7 +2527,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,12 +2578,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RIR</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>RIR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SRIT</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>SRIT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2714,12 +2714,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2748,12 +2748,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2765,7 +2765,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UGARSUGAR</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,24 +2884,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CINEVISTA</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3054,7 +3054,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3156,12 +3156,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HUHTAMAKI</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3224,12 +3224,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3241,12 +3241,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3326,7 +3326,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3360,12 +3360,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KNACK</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3496,12 +3496,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -3513,12 +3513,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MARALOVER</t>
+          <t>KNACK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3530,7 +3530,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>NIITLTD</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>MARALOVER</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>MARATHON</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3649,12 +3649,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3666,7 +3666,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,7 +3700,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>NIITLTD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SECMARK</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3836,7 +3836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,12 +3887,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -3904,12 +3904,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3938,12 +3938,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3955,12 +3955,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3972,12 +3972,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4050,31 +4050,31 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4084,99 +4084,99 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>APCOTEXIND</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4220,14 +4220,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4237,14 +4237,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4254,14 +4254,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4271,19 +4271,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BOROSCI</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4295,12 +4295,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4312,7 +4312,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CHEMFAB</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4380,7 +4380,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4397,7 +4397,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4465,7 +4465,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4499,7 +4499,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4516,7 +4516,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4533,12 +4533,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4550,12 +4550,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4567,7 +4567,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4584,7 +4584,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4618,12 +4618,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -4669,12 +4669,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -4686,12 +4686,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4737,12 +4737,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4788,7 +4788,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>GLFL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -4822,12 +4822,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4890,12 +4890,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4941,7 +4941,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -4975,12 +4975,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -4992,12 +4992,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5009,12 +5009,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SHILCTECH</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5043,12 +5043,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5060,7 +5060,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SNOWMAN</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5077,7 +5077,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5111,12 +5111,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5230,12 +5230,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -5247,7 +5247,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5264,12 +5264,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5298,24 +5298,24 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5359,31 +5359,31 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5393,48 +5393,48 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5444,31 +5444,31 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5478,31 +5478,31 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>SHILCTECH</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5512,31 +5512,31 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>SNOWMAN</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5546,14 +5546,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5563,65 +5563,65 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5631,14 +5631,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5648,31 +5648,31 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>FIBERWEB</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5682,48 +5682,48 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5750,31 +5750,31 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>HORIZONIND</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5784,36 +5784,36 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -5825,12 +5825,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5876,12 +5876,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>ALLDIGI</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -5893,7 +5893,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5910,12 +5910,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -5927,7 +5927,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5944,12 +5944,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6046,12 +6046,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -6097,12 +6097,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -6114,12 +6114,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -6131,12 +6131,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SURAJLTD</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6165,12 +6165,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -6182,7 +6182,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6199,12 +6199,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6284,12 +6284,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>FIBERWEB</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -6301,12 +6301,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6328,14 +6328,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6345,48 +6345,48 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>GENUSPAPER</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>HORIZONIND</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6498,31 +6498,31 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6532,14 +6532,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDOSTAR</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6549,14 +6549,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6566,14 +6566,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6583,82 +6583,82 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6685,14 +6685,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6702,14 +6702,14 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6719,48 +6719,48 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>NAHARCAP</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>NAHARPOLY</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>NAHARSPING</t>
+          <t>NIITMTS</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6770,31 +6770,31 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6838,48 +6838,48 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6889,31 +6889,31 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6923,14 +6923,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6940,65 +6940,65 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -7008,31 +7008,31 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>SURAJLTD</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7042,14 +7042,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7059,31 +7059,31 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7093,14 +7093,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -7144,31 +7144,31 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>VEDPOWER</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -7178,14 +7178,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,65 +7195,65 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>VOGL</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7280,31 +7280,31 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,14 +7331,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7348,31 +7348,31 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,14 +7382,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7399,31 +7399,31 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7467,14 +7467,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,48 +7484,48 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>EMAMIPAP</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -7552,14 +7552,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7569,31 +7569,31 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7620,31 +7620,31 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>HLVLTD</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7654,14 +7654,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7688,31 +7688,31 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7739,14 +7739,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7756,14 +7756,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7790,14 +7790,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7807,65 +7807,65 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>NAHARPOLY</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>NAHARSPING</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>NORBTEAEXP</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7875,31 +7875,31 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MIRZAINT</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,31 +7943,31 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7977,31 +7977,31 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -8011,48 +8011,48 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -8062,31 +8062,31 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,48 +8096,48 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ASHIANA</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>CPL</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -8198,14 +8198,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -8232,48 +8232,48 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,31 +8283,31 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -8334,65 +8334,65 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>SAHYADRI</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -8419,31 +8419,31 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -8453,65 +8453,65 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -8538,14 +8538,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -8555,31 +8555,31 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -8589,31 +8589,31 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>FLAIR</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -8623,48 +8623,48 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -8674,31 +8674,31 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -8708,14 +8708,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>UNIVCABLES</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -8725,14 +8725,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -8742,14 +8742,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -8759,65 +8759,65 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -8827,14 +8827,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -8844,14 +8844,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -8861,48 +8861,48 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -8912,31 +8912,31 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -8963,48 +8963,48 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -9014,14 +9014,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -9031,14 +9031,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -9048,14 +9048,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -9065,31 +9065,31 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -9099,48 +9099,48 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -9150,14 +9150,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -9167,31 +9167,31 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -9218,14 +9218,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -9235,14 +9235,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -9252,14 +9252,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -9269,31 +9269,31 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>TRANSWORLD</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -9303,31 +9303,31 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>HEGAM</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR</t>
+          <t>IL&amp;FSENGG</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -9337,65 +9337,65 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>MIRZAINT</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -9422,14 +9422,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NRAIL</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -9473,14 +9473,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>GILLETTE</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -9507,14 +9507,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -9524,22 +9524,2045 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
+          <t>RML</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>RUSHIL</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>SERVOTECH</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>SHALBY</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>AGOL</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>ALLTIME</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>ASHIANA</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>BASF</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>CARYSIL</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>ENTERO</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>ESABINDIA</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend/Other business matters</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>JMFINANCIL</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>JTEKTINDIA</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>JYOTHYLAB</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>KANSAINER</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>KSHINTL</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>MITTAL</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>NAVKARURB</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ORKLAINDIA</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>RUSTOMJEE</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>SANATHAN</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>SAURASHCEM</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>UNIVCABLES</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>EXCELSOFT</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>GAYAHWS</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>GOACARBON</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>GUJENERGY</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>KMSUGAR</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>MFML</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>MUTHOOTCAP</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>BANCOINDIA</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>CITIUSINVT</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>KAKATCEM</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>KCP</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>TRANSWORLD</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>SUPRAJIT</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>CENTRUM</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>GILLETTE</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
           <t>MTNL</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C593"/>
+  <dimension ref="A1:C713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Buyback</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SIYSIL</t>
+          <t>SHAHINVEST</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>SIYSIL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VISL</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VSSL</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>VSSL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3207,29 +3207,29 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>20MICRONS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ADROITIND</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3309,12 +3309,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>ADROITIND</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3326,12 +3326,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3343,12 +3343,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3360,12 +3360,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>APCOTEXIND</t>
+          <t>AIFL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>ARKADE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BOROSCI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3513,7 +3513,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHEMFAB</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3530,12 +3530,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3564,7 +3564,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DIAMINESQ</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3666,12 +3666,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3700,7 +3700,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3717,7 +3717,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GLFL</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>FABTECH</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>GLFL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>GOODLUCK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3836,7 +3836,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>GRPLTD</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>INFOBEAN</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3904,12 +3904,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3938,12 +3938,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3955,7 +3955,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3972,12 +3972,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4023,7 +4023,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4040,12 +4040,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NITYAS</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4142,12 +4142,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4176,12 +4176,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4193,7 +4193,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>NITYAS</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4244,12 +4244,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4261,12 +4261,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4295,12 +4295,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4312,7 +4312,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4346,12 +4346,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4380,7 +4380,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SEITINVIT</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4397,7 +4397,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SHALPAINTS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SHILCTECH</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4431,12 +4431,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -4448,12 +4448,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SNOWMAN</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -4465,7 +4465,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SUDARCOLOR</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -4516,12 +4516,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4533,12 +4533,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>SCILAL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4550,12 +4550,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>SEITINVIT</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4567,7 +4567,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>SHALPAINTS</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4584,7 +4584,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>SHILCTECH</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4618,12 +4618,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>SNOWMAN</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>VAML</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>SUDARCOLOR</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4686,7 +4686,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ZOTA</t>
+          <t>TALWALKARS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4747,31 +4747,31 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4781,14 +4781,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ALLDIGI</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4815,31 +4815,31 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>VAKRANGEE</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4849,14 +4849,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4866,48 +4866,48 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>VARDHACRLC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4934,65 +4934,65 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>ZOTA</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5009,12 +5009,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5026,12 +5026,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5043,7 +5043,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5060,12 +5060,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>ALLDIGI</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5077,7 +5077,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5094,12 +5094,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>ARCIL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5145,12 +5145,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5162,12 +5162,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Fund Raising</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5213,12 +5213,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FIBERWEB</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5230,7 +5230,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>FINOPB</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5264,7 +5264,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>GENUSPAPER</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5298,12 +5298,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -5315,12 +5315,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -5332,7 +5332,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5349,12 +5349,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -5366,12 +5366,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>HORIZONIND</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5400,12 +5400,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5417,7 +5417,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>INDOSTAR</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>EPACK</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>FIBERWEB</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5553,7 +5553,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>FINOPB</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -5587,7 +5587,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5604,7 +5604,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GENUSPAPER</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5655,12 +5655,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MONARCH</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Financial Results/Stock Split</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5689,7 +5689,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>NIITMTS</t>
+          <t>HEIDELBERG</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5706,7 +5706,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>HORIZONIND</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5723,7 +5723,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5740,7 +5740,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5791,12 +5791,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>INDOSTAR</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5825,12 +5825,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5876,12 +5876,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -5893,7 +5893,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5910,12 +5910,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>STEAMHOUSE</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -5944,7 +5944,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>SURAJLTD</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5961,7 +5961,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>MONARCH</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Stock Split</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6046,12 +6046,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>NIITMTS</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TIPSFILMS</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6097,12 +6097,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>VEDPOWER</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -6114,7 +6114,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>VOGL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6165,7 +6165,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6182,24 +6182,24 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6209,31 +6209,31 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6243,31 +6243,31 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>SENORES</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6294,31 +6294,31 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6328,31 +6328,31 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6362,14 +6362,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>STEAMHOUSE</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>SURAJLTD</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>EMAMIPAP</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6464,14 +6464,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>GLOBUSSPR</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6532,14 +6532,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6549,14 +6549,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>VEDPOWER</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6566,14 +6566,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>HLVLTD</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6583,31 +6583,31 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>VOGL</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6651,19 +6651,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>LCCPROJECT</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -6675,7 +6675,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>NAHARCAP</t>
+          <t>ADVAIT</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6743,7 +6743,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>NAHARPOLY</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6760,12 +6760,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>NAHARSPING</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -6777,12 +6777,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6794,12 +6794,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>NORBTEAEXP</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -6811,7 +6811,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6828,7 +6828,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6879,7 +6879,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>SHREERAMA</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6913,7 +6913,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6930,7 +6930,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6947,12 +6947,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>DCMNVL</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -6964,12 +6964,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -6981,7 +6981,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>DIGIDRIVE</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6998,12 +6998,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -7015,7 +7015,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7032,7 +7032,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>DYNPRO</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ATULAUTO</t>
+          <t>EMAMIPAP</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7076,31 +7076,31 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CPL</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>DLINKINDIA</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>GANGOTRI</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -7178,14 +7178,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>GOCOLORS</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7212,31 +7212,31 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>LGBBROSLTD</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>HLVLTD</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7246,14 +7246,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7280,14 +7280,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>NUCLEUS</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7297,31 +7297,31 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>SAHYADRI</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7331,14 +7331,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7348,31 +7348,31 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>SHYAMMETL</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>LCCPROJECT</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7382,48 +7382,48 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>BCLIND</t>
+          <t>MALUPAPER</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7467,14 +7467,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>DIGITIDE</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7484,48 +7484,48 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>NAHARPOLY</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>NAHARSPING</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>FLAIR</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>NIACL</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -7552,14 +7552,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>NILASPACES</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>NORBTEAEXP</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -7586,14 +7586,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>HECPROJECT</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7603,31 +7603,31 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7637,31 +7637,31 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>IFBAGRO</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7688,82 +7688,82 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MINDSPACE</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7790,14 +7790,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7807,31 +7807,31 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7841,31 +7841,31 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>SHK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7875,31 +7875,31 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>TTKHLTCARE</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TVTODAY</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7943,48 +7943,48 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>WONDERLA</t>
+          <t>UEL</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ZUARI</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7994,14 +7994,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -8011,14 +8011,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>WORTHPERI</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -8028,48 +8028,48 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>XCHANGING</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ZODIAC</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>ATULAUTO</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -8096,48 +8096,48 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>CPL</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -8181,31 +8181,31 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>DLINKINDIA</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>GSPLTRANS</t>
+          <t>EVEREADY</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>GANGOTRI</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -8232,31 +8232,31 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>HEGAM</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>IL&amp;FSENGG</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -8266,14 +8266,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -8283,31 +8283,31 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>LGBBROSLTD</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -8334,14 +8334,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>MIRZAINT</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -8351,116 +8351,116 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>NEPHROPLUS</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>NUCLEUS</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>PODDARMENT</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>PUNJABCHEM</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>SAHYADRI</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -8470,14 +8470,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -8487,14 +8487,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -8504,31 +8504,31 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>SHALBY</t>
+          <t>TTL</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -8538,48 +8538,48 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>ZENTEC</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>AGOL</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -8589,14 +8589,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>BCLIND</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -8606,48 +8606,48 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BIRLANU</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>ASHIANA</t>
+          <t>BPL</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -8657,14 +8657,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -8674,31 +8674,31 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CARYSIL</t>
+          <t>DIGITIDE</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -8708,48 +8708,48 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>FLAIR</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -8776,31 +8776,31 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -8810,48 +8810,48 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>GOPAL</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend/Other business matters</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>ESABINDIA</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -8861,48 +8861,48 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>HECPROJECT</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -8912,31 +8912,31 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -8963,14 +8963,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -8980,14 +8980,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>JTEKTINDIA</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8997,31 +8997,31 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>KKCL</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -9031,65 +9031,65 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>MINDSPACE</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -9099,14 +9099,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -9116,31 +9116,31 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -9150,14 +9150,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -9184,31 +9184,31 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>PSPPROJECT</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -9218,14 +9218,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -9235,48 +9235,48 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SHEMAROO</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>RUSTOMJEE</t>
+          <t>SHK</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -9286,14 +9286,14 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -9303,31 +9303,31 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>TVTODAY</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -9337,31 +9337,31 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>WALCHANNAG</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>UNIVCABLES</t>
+          <t>WONDERLA</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -9371,14 +9371,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>ZUARI</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -9388,14 +9388,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -9422,48 +9422,48 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>AMAGI</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -9473,14 +9473,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -9507,14 +9507,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -9524,31 +9524,31 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -9558,14 +9558,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>DENORA</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -9575,14 +9575,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -9592,31 +9592,31 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -9626,14 +9626,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -9643,14 +9643,14 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>KMSUGAR</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -9677,48 +9677,48 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>HEGAM</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising/Other business matters</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IL&amp;FSENGG</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -9728,14 +9728,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -9745,14 +9745,14 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MUTHOOTCAP</t>
+          <t>KOTHARIPET</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -9762,14 +9762,14 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -9779,14 +9779,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -9796,14 +9796,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -9813,14 +9813,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>MASTERTR</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -9830,14 +9830,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -9847,14 +9847,14 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>MIRZAINT</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -9864,14 +9864,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>MONTECARLO</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -9881,48 +9881,48 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>UGROCAP</t>
+          <t>NEPHROPLUS</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>NRAIL</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -9932,14 +9932,14 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>PUNJABCHEM</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -9966,65 +9966,65 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CITIUSINVT</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -10034,14 +10034,14 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>ELGIEQUIP</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -10051,31 +10051,31 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>SHALBY</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -10085,65 +10085,65 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>SPECIALITY</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -10170,48 +10170,48 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>TRANSWORLD</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>AGOL</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -10221,65 +10221,65 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>GOLDIAM</t>
+          <t>ASHIANA</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>ATLANTAA</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -10289,14 +10289,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -10306,14 +10306,14 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -10323,31 +10323,31 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>CAPACITE</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -10357,48 +10357,48 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>RANEHOLDIN</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -10408,31 +10408,31 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -10442,14 +10442,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>GILLETTE</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -10459,14 +10459,14 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -10476,24 +10476,2064 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
+          <t>ESABINDIA</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>GKSL</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>GMMPFAUDLR</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend/Other business matters</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>GRSE</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>JKLAKSHMI</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>JMFINANCIL</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>JTEKTINDIA</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>JYOTHYLAB</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>KANSAINER</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>KSHINTL</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>MINDTECK</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>MITTAL</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>NAVKARURB</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>ORKLAINDIA</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>RUSTOMJEE</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>RVTH</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>SANATHAN</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>SAURASHCEM</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>SIS</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>UNICHEMLAB</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>UNIVCABLES</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>AGARWALEYE</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>AMAGI</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>BIRLACABLE</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>EXCELSOFT</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>GAYAHWS</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>GOACARBON</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>GUJENERGY</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>KMSUGAR</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>KOTARISUG</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>LXCHEM</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>MFML</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>MUTHOOTCAP</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>ORIENTPPR</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>ROADSTAR</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>TCPLPACK</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>VSTTILLERS</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>BANCOINDIA</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>CITIUSINVT</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>COFFEEDAY</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>KAKATCEM</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>KCP</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>TRANSWORLD</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>GOLDIAM</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>SUPRAJIT</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>BASML</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>RANEHOLDIN</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>BALAJITELE</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>CENTRUM</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>GILLETTE</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
           <t>MTNL</t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
         <is>
           <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
         </is>
       </c>
     </row>
